--- a/assets/Item_Code_allocation_table.xlsx
+++ b/assets/Item_Code_allocation_table.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://earthboundtradingcom-my.sharepoint.com/personal/wesley_earthboundtrading_com/Documents/Desktop/EBT_AI_Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="37" documentId="8_{F098BD13-B334-45D3-82A1-EBDD3E29AFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{039CBFE3-26F5-40D9-BC0A-D19A35F2ECDB}"/>

--- a/assets/Item_Code_allocation_table.xlsx
+++ b/assets/Item_Code_allocation_table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://earthboundtradingcom-my.sharepoint.com/personal/wesley_earthboundtrading_com/Documents/Desktop/EBT_AI_Project/Tables/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="8_{F098BD13-B334-45D3-82A1-EBDD3E29AFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{783EEB2E-8C2C-4BB9-B292-1A7BF6DA2FE9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3769F34E-020E-4788-A40D-F4190A44D801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="764" xr2:uid="{09BBBF33-EBB5-4EDB-9CE7-7EB6A33B148E}"/>
   </bookViews>

--- a/assets/Item_Code_allocation_table.xlsx
+++ b/assets/Item_Code_allocation_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wesley\Documents\WebOrderAI\weborder-ai\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3769F34E-020E-4788-A40D-F4190A44D801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1D1CE2-4284-4222-9EE3-0AAC42994FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="764" xr2:uid="{09BBBF33-EBB5-4EDB-9CE7-7EB6A33B148E}"/>
   </bookViews>
@@ -1063,25 +1063,25 @@
         <v>98600</v>
       </c>
       <c r="B22" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C22" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D22" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E22" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F22" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G22" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H22" s="4">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -1089,25 +1089,25 @@
         <v>98601</v>
       </c>
       <c r="B23" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C23" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D23" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E23" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F23" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G23" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H23" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
